--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N171_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N171_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>51.22207267775109</v>
+        <v>8.323586810134552</v>
       </c>
       <c r="D2" t="n">
-        <v>49.07640805071713</v>
+        <v>7.974916308241535</v>
       </c>
       <c r="E2" t="n">
-        <v>6.983620272890729</v>
+        <v>1.134838294344743</v>
       </c>
       <c r="F2" t="n">
-        <v>11.44132591097767</v>
+        <v>1.859215460533871</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>61.15287614029018</v>
+        <v>9.937342372797154</v>
       </c>
       <c r="D3" t="n">
-        <v>41.40823087895649</v>
+        <v>6.72883751783043</v>
       </c>
       <c r="E3" t="n">
-        <v>6.983620272890729</v>
+        <v>1.134838294344743</v>
       </c>
       <c r="F3" t="n">
-        <v>11.44132591097767</v>
+        <v>1.859215460533871</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>41.23611160363697</v>
+        <v>6.700868135591008</v>
       </c>
       <c r="D4" t="n">
-        <v>21.84562288572759</v>
+        <v>3.549913718930734</v>
       </c>
       <c r="E4" t="n">
-        <v>6.983620272890729</v>
+        <v>1.134838294344743</v>
       </c>
       <c r="F4" t="n">
-        <v>11.44132591097767</v>
+        <v>1.859215460533871</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>44.41227716790704</v>
+        <v>7.216995039784894</v>
       </c>
       <c r="D5" t="n">
-        <v>44.54072923090803</v>
+        <v>7.237868500022556</v>
       </c>
       <c r="E5" t="n">
-        <v>6.983620272890729</v>
+        <v>1.134838294344743</v>
       </c>
       <c r="F5" t="n">
-        <v>11.44132591097767</v>
+        <v>1.859215460533871</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>54.46378689121463</v>
+        <v>8.850365369822377</v>
       </c>
       <c r="D6" t="n">
-        <v>54.65903788833278</v>
+        <v>8.882093656854076</v>
       </c>
       <c r="E6" t="n">
-        <v>6.983620272890729</v>
+        <v>1.134838294344743</v>
       </c>
       <c r="F6" t="n">
-        <v>11.44132591097767</v>
+        <v>1.859215460533871</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>57.42813765772577</v>
+        <v>9.332072369380437</v>
       </c>
       <c r="D7" t="n">
-        <v>56.27285048035311</v>
+        <v>9.14433820305738</v>
       </c>
       <c r="E7" t="n">
-        <v>6.983620272890729</v>
+        <v>1.134838294344743</v>
       </c>
       <c r="F7" t="n">
-        <v>11.44132591097767</v>
+        <v>1.859215460533871</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
